--- a/output/tables/afs_facilities_table.xlsx
+++ b/output/tables/afs_facilities_table.xlsx
@@ -92,7 +92,7 @@
     <t xml:space="preserve">A - Major: actual/potential emissions above major source thresholds</t>
   </si>
   <si>
-    <t xml:space="preserve">C - Unknown</t>
+    <t xml:space="preserve">C - Unregulated pollutant: actual/potential controlled emissions &gt;100 tons/year</t>
   </si>
   <si>
     <t xml:space="preserve">ND - Thresholds not defined</t>
@@ -133,7 +133,7 @@
 EPA compliance status code for the facility.</t>
   </si>
   <si>
-    <t xml:space="preserve">C</t>
+    <t xml:space="preserve">C - In Compliance With Procedural Requirements</t>
   </si>
   <si>
     <t xml:space="preserve">3 - In Compliance, Inspection</t>
